--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130140341</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130140332</v>
+        <v>130140311</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>97704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633843</v>
+        <v>633784</v>
       </c>
       <c r="R3" t="n">
-        <v>6658899</v>
+        <v>6658954</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140311</v>
+        <v>130140332</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633784</v>
+        <v>633843</v>
       </c>
       <c r="R4" t="n">
-        <v>6658954</v>
+        <v>6658899</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130140338</v>
+        <v>130140314</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>97704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633847</v>
+        <v>633771</v>
       </c>
       <c r="R7" t="n">
-        <v>6658901</v>
+        <v>6659042</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130140314</v>
+        <v>130140338</v>
       </c>
       <c r="B8" t="n">
-        <v>97702</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633771</v>
+        <v>633847</v>
       </c>
       <c r="R8" t="n">
-        <v>6659042</v>
+        <v>6658901</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
         <v>130140330</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130140342</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130140334</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>130140313</v>
       </c>
       <c r="B15" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140294</v>
+        <v>130140328</v>
       </c>
       <c r="B17" t="n">
-        <v>97077</v>
+        <v>98833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633844</v>
+        <v>633864</v>
       </c>
       <c r="R17" t="n">
-        <v>6658910</v>
+        <v>6658889</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2231,6 +2231,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2257,32 +2262,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140328</v>
+        <v>130140294</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>97079</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2292,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633864</v>
+        <v>633844</v>
       </c>
       <c r="R18" t="n">
-        <v>6658889</v>
+        <v>6658910</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2328,11 +2333,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,7 +2362,7 @@
         <v>130140293</v>
       </c>
       <c r="B19" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>130140324</v>
       </c>
       <c r="B20" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>130140335</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130140341</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130140311</v>
+        <v>130140332</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633784</v>
+        <v>633843</v>
       </c>
       <c r="R3" t="n">
-        <v>6658954</v>
+        <v>6658899</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140332</v>
+        <v>130140311</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633843</v>
+        <v>633784</v>
       </c>
       <c r="R4" t="n">
-        <v>6658899</v>
+        <v>6658954</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>130140306</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130140301</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130140314</v>
       </c>
       <c r="B7" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>130140338</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130140304</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>130140330</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>130140305</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>130140308</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130140342</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130140334</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>130140313</v>
       </c>
       <c r="B15" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>130140302</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140328</v>
+        <v>130140294</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>97166</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633864</v>
+        <v>633844</v>
       </c>
       <c r="R17" t="n">
-        <v>6658889</v>
+        <v>6658910</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2231,11 +2231,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2262,32 +2257,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140294</v>
+        <v>130140328</v>
       </c>
       <c r="B18" t="n">
-        <v>97079</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633844</v>
+        <v>633864</v>
       </c>
       <c r="R18" t="n">
-        <v>6658910</v>
+        <v>6658889</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2333,6 +2328,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,7 +2362,7 @@
         <v>130140293</v>
       </c>
       <c r="B19" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>130140324</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>130140335</v>
       </c>
       <c r="B21" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140328</v>
+        <v>130140294</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633864</v>
+        <v>633844</v>
       </c>
       <c r="R17" t="n">
-        <v>6658889</v>
+        <v>6658910</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2231,11 +2231,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2262,32 +2257,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140294</v>
+        <v>130140328</v>
       </c>
       <c r="B18" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633844</v>
+        <v>633864</v>
       </c>
       <c r="R18" t="n">
-        <v>6658910</v>
+        <v>6658889</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2333,6 +2328,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140294</v>
+        <v>130140328</v>
       </c>
       <c r="B17" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633844</v>
+        <v>633864</v>
       </c>
       <c r="R17" t="n">
-        <v>6658910</v>
+        <v>6658889</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2231,6 +2231,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2257,32 +2262,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140328</v>
+        <v>130140294</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2292,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633864</v>
+        <v>633844</v>
       </c>
       <c r="R18" t="n">
-        <v>6658889</v>
+        <v>6658910</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2328,11 +2333,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130140311</v>
+        <v>130140332</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633784</v>
+        <v>633843</v>
       </c>
       <c r="R3" t="n">
-        <v>6658954</v>
+        <v>6658899</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140332</v>
+        <v>130140311</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633843</v>
+        <v>633784</v>
       </c>
       <c r="R4" t="n">
-        <v>6658899</v>
+        <v>6658954</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130140314</v>
+        <v>130140338</v>
       </c>
       <c r="B7" t="n">
-        <v>97791</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633771</v>
+        <v>633847</v>
       </c>
       <c r="R7" t="n">
-        <v>6659042</v>
+        <v>6658901</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130140338</v>
+        <v>130140314</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>97791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633847</v>
+        <v>633771</v>
       </c>
       <c r="R8" t="n">
-        <v>6658901</v>
+        <v>6659042</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130140341</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130140332</v>
+        <v>130140311</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>97794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633843</v>
+        <v>633784</v>
       </c>
       <c r="R3" t="n">
-        <v>6658899</v>
+        <v>6658954</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140311</v>
+        <v>130140332</v>
       </c>
       <c r="B4" t="n">
-        <v>97791</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633784</v>
+        <v>633843</v>
       </c>
       <c r="R4" t="n">
-        <v>6658954</v>
+        <v>6658899</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130140338</v>
+        <v>130140314</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>97794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633847</v>
+        <v>633771</v>
       </c>
       <c r="R7" t="n">
-        <v>6658901</v>
+        <v>6659042</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130140314</v>
+        <v>130140338</v>
       </c>
       <c r="B8" t="n">
-        <v>97791</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633771</v>
+        <v>633847</v>
       </c>
       <c r="R8" t="n">
-        <v>6659042</v>
+        <v>6658901</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
         <v>130140330</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130140342</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>130140334</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>130140313</v>
       </c>
       <c r="B15" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140328</v>
+        <v>130140294</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>97169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633864</v>
+        <v>633844</v>
       </c>
       <c r="R17" t="n">
-        <v>6658889</v>
+        <v>6658910</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2231,11 +2231,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2262,32 +2257,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140294</v>
+        <v>130140328</v>
       </c>
       <c r="B18" t="n">
-        <v>97166</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633844</v>
+        <v>633864</v>
       </c>
       <c r="R18" t="n">
-        <v>6658910</v>
+        <v>6658889</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2333,6 +2328,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,7 +2362,7 @@
         <v>130140293</v>
       </c>
       <c r="B19" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>130140324</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>130140335</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130140341</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130140311</v>
+        <v>130140332</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633784</v>
+        <v>633843</v>
       </c>
       <c r="R3" t="n">
-        <v>6658954</v>
+        <v>6658899</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140332</v>
+        <v>130140311</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>97820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633843</v>
+        <v>633784</v>
       </c>
       <c r="R4" t="n">
-        <v>6658899</v>
+        <v>6658954</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>130140306</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130140301</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130140314</v>
+        <v>130140338</v>
       </c>
       <c r="B7" t="n">
-        <v>97794</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633771</v>
+        <v>633847</v>
       </c>
       <c r="R7" t="n">
-        <v>6659042</v>
+        <v>6658901</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130140338</v>
+        <v>130140314</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>97820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633847</v>
+        <v>633771</v>
       </c>
       <c r="R8" t="n">
-        <v>6658901</v>
+        <v>6659042</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,7 +1372,7 @@
         <v>130140304</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>130140330</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>130140305</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>130140308</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130140342</v>
+        <v>130140334</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633838</v>
+        <v>633837</v>
       </c>
       <c r="R13" t="n">
-        <v>6658903</v>
+        <v>6658892</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 buketter 1127</t>
+          <t>2 buketter 1133</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140334</v>
+        <v>130140342</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633837</v>
+        <v>633838</v>
       </c>
       <c r="R14" t="n">
-        <v>6658892</v>
+        <v>6658903</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 buketter 1133</t>
+          <t>10 buketter 1127</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,7 +1969,7 @@
         <v>130140313</v>
       </c>
       <c r="B15" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>130140302</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>130140294</v>
       </c>
       <c r="B17" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>130140328</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>130140293</v>
       </c>
       <c r="B19" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140324</v>
+        <v>130140335</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633851</v>
+        <v>633823</v>
       </c>
       <c r="R20" t="n">
-        <v>6658902</v>
+        <v>6658918</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>6 buketter 1143</t>
+          <t>18 buketter 1152</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140335</v>
+        <v>130140324</v>
       </c>
       <c r="B21" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633823</v>
+        <v>633851</v>
       </c>
       <c r="R21" t="n">
-        <v>6658918</v>
+        <v>6658902</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>18 buketter 1152</t>
+          <t>6 buketter 1143</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130140341</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130140332</v>
+        <v>130140311</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>97821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633843</v>
+        <v>633784</v>
       </c>
       <c r="R3" t="n">
-        <v>6658899</v>
+        <v>6658954</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140311</v>
+        <v>130140332</v>
       </c>
       <c r="B4" t="n">
-        <v>97820</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633784</v>
+        <v>633843</v>
       </c>
       <c r="R4" t="n">
-        <v>6658954</v>
+        <v>6658899</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1173,7 +1173,7 @@
         <v>130140338</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>130140314</v>
       </c>
       <c r="B8" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>130140330</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130140334</v>
+        <v>130140342</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633837</v>
+        <v>633838</v>
       </c>
       <c r="R13" t="n">
-        <v>6658892</v>
+        <v>6658903</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 buketter 1133</t>
+          <t>10 buketter 1127</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140342</v>
+        <v>130140334</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633838</v>
+        <v>633837</v>
       </c>
       <c r="R14" t="n">
-        <v>6658903</v>
+        <v>6658892</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>10 buketter 1127</t>
+          <t>2 buketter 1133</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,7 +1969,7 @@
         <v>130140313</v>
       </c>
       <c r="B15" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>130140294</v>
       </c>
       <c r="B17" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>130140328</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>130140293</v>
       </c>
       <c r="B19" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140335</v>
+        <v>130140324</v>
       </c>
       <c r="B20" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633823</v>
+        <v>633851</v>
       </c>
       <c r="R20" t="n">
-        <v>6658918</v>
+        <v>6658902</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>18 buketter 1152</t>
+          <t>6 buketter 1143</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140324</v>
+        <v>130140335</v>
       </c>
       <c r="B21" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633851</v>
+        <v>633823</v>
       </c>
       <c r="R21" t="n">
-        <v>6658902</v>
+        <v>6658918</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>6 buketter 1143</t>
+          <t>18 buketter 1152</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>130344246</v>
       </c>
       <c r="B22" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130344247</v>
       </c>
       <c r="B23" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>130344245</v>
       </c>
       <c r="B24" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 62004-2025 artfynd.xlsx
+++ b/artfynd/A 62004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130140341</v>
+        <v>130140293</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
         <v>633852</v>
       </c>
       <c r="R2" t="n">
-        <v>6658880</v>
+        <v>6658932</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>10 buketter 1136</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130140311</v>
+        <v>130140294</v>
       </c>
       <c r="B3" t="n">
-        <v>97821</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633784</v>
+        <v>633844</v>
       </c>
       <c r="R3" t="n">
-        <v>6658954</v>
+        <v>6658910</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140332</v>
+        <v>130140301</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633843</v>
+        <v>633731</v>
       </c>
       <c r="R4" t="n">
-        <v>6658899</v>
+        <v>6658997</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130140306</v>
+        <v>130140302</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633798</v>
+        <v>633646</v>
       </c>
       <c r="R5" t="n">
-        <v>6658884</v>
+        <v>6658980</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130140301</v>
+        <v>130140304</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633731</v>
+        <v>633868</v>
       </c>
       <c r="R6" t="n">
-        <v>6658997</v>
+        <v>6658895</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1170,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130140338</v>
+        <v>130140305</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633847</v>
+        <v>633839</v>
       </c>
       <c r="R7" t="n">
-        <v>6658901</v>
+        <v>6658908</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130140314</v>
+        <v>130140306</v>
       </c>
       <c r="B8" t="n">
-        <v>97821</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633771</v>
+        <v>633798</v>
       </c>
       <c r="R8" t="n">
-        <v>6659042</v>
+        <v>6658884</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1369,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130140304</v>
+        <v>130140308</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1404,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633868</v>
+        <v>633861</v>
       </c>
       <c r="R9" t="n">
-        <v>6658895</v>
+        <v>6658868</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1466,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130140330</v>
+        <v>130140321</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633844</v>
+        <v>633764</v>
       </c>
       <c r="R10" t="n">
-        <v>6658900</v>
+        <v>6658776</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1541,7 +1526,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>30 buketter 1131</t>
+          <t>8 buketter 1224</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130140305</v>
+        <v>130140324</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633839</v>
+        <v>633851</v>
       </c>
       <c r="R11" t="n">
-        <v>6658908</v>
+        <v>6658902</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1639,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6 buketter 1143</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130140308</v>
+        <v>130140328</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633861</v>
+        <v>633864</v>
       </c>
       <c r="R12" t="n">
-        <v>6658868</v>
+        <v>6658889</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 buketter 1141</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130140342</v>
+        <v>130140330</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633838</v>
+        <v>633844</v>
       </c>
       <c r="R13" t="n">
-        <v>6658903</v>
+        <v>6658900</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1837,7 +1832,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 buketter 1127</t>
+          <t>30 buketter 1131</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140334</v>
+        <v>130140332</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633837</v>
+        <v>633843</v>
       </c>
       <c r="R14" t="n">
-        <v>6658892</v>
+        <v>6658899</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1939,7 +1934,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 buketter 1133</t>
+          <t>20 buketter 1132</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,32 +1961,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130140313</v>
+        <v>130140333</v>
       </c>
       <c r="B15" t="n">
-        <v>97821</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633833</v>
+        <v>633809</v>
       </c>
       <c r="R15" t="n">
-        <v>6658891</v>
+        <v>6658768</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2037,6 +2032,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 buketter 1209</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2063,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140302</v>
+        <v>130140334</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633646</v>
+        <v>633837</v>
       </c>
       <c r="R16" t="n">
-        <v>6658980</v>
+        <v>6658892</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2134,6 +2134,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 buketter 1133</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2160,32 +2165,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140294</v>
+        <v>130140335</v>
       </c>
       <c r="B17" t="n">
-        <v>97196</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633844</v>
+        <v>633823</v>
       </c>
       <c r="R17" t="n">
-        <v>6658910</v>
+        <v>6658918</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2231,6 +2236,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>18 buketter 1152</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2257,10 +2267,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140328</v>
+        <v>130140337</v>
       </c>
       <c r="B18" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633864</v>
+        <v>633805</v>
       </c>
       <c r="R18" t="n">
-        <v>6658889</v>
+        <v>6658776</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2332,7 +2342,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4 buketter 1141</t>
+          <t>15 buketter 1208</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2359,32 +2369,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130140293</v>
+        <v>130140338</v>
       </c>
       <c r="B19" t="n">
-        <v>97196</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2394,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633852</v>
+        <v>633847</v>
       </c>
       <c r="R19" t="n">
-        <v>6658932</v>
+        <v>6658901</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2430,6 +2440,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 buketter 1130</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2456,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140324</v>
+        <v>130140341</v>
       </c>
       <c r="B20" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633851</v>
+        <v>633852</v>
       </c>
       <c r="R20" t="n">
-        <v>6658902</v>
+        <v>6658880</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,7 +2546,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>6 buketter 1143</t>
+          <t>10 buketter 1136</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2558,10 +2573,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140335</v>
+        <v>130140342</v>
       </c>
       <c r="B21" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633823</v>
+        <v>633838</v>
       </c>
       <c r="R21" t="n">
-        <v>6658918</v>
+        <v>6658903</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2633,7 +2648,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>18 buketter 1152</t>
+          <t>10 buketter 1127</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2660,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130344246</v>
+        <v>130294383</v>
       </c>
       <c r="B22" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,29 +2703,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633825</v>
+        <v>633761</v>
       </c>
       <c r="R22" t="n">
-        <v>6658891</v>
+        <v>6658790</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2734,27 +2740,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>skott</t>
+          <t>4 bujetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2769,22 +2765,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130344247</v>
+        <v>130344245</v>
       </c>
       <c r="B23" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2811,7 +2807,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2825,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633816</v>
+        <v>633810</v>
       </c>
       <c r="R23" t="n">
-        <v>6658880</v>
+        <v>6658886</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2860,7 +2856,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2870,7 +2866,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2902,10 +2898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130344245</v>
+        <v>130344246</v>
       </c>
       <c r="B24" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,7 +2928,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2946,10 +2942,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633810</v>
+        <v>633825</v>
       </c>
       <c r="R24" t="n">
-        <v>6658886</v>
+        <v>6658891</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2981,7 +2977,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2991,7 +2987,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3020,6 +3016,418 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130344247</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>633816</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6658880</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>skott</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130140311</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633784</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6658954</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130140313</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>633833</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6658891</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130140314</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>633771</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6659042</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
